--- a/詳細設計/01D_バッチ詳細設計書テンプレート.xlsx
+++ b/詳細設計/01D_バッチ詳細設計書テンプレート.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="Rd176eb6dd26c433c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="Rccd8f7c5c4134389"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_Batch概要・起動" sheetId="3" r:id="Rc76753e5d3944712"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_入出力・Parameter" sheetId="4" r:id="R0f32161ae72449e7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_処理業務フロー" sheetId="5" r:id="Rfb3be4c3fadf49da"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_SQL・Transaction" sheetId="6" r:id="R6fab578c2cb54276"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_Restart・例外・Log" sheetId="7" r:id="R32aa14297ae34d7f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_単体テスト観点" sheetId="8" r:id="Ra8aa2b6b85684a9e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="R25143bb76a4341a5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="R305b514309844bb6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_Batch概要・起動" sheetId="3" r:id="R39e80dcff4b34056"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_入出力・Parameter" sheetId="4" r:id="R4ceda2cd43e54cd4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_処理業務フロー" sheetId="5" r:id="R3f77a2061b294b7b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_SQL・Transaction" sheetId="6" r:id="Rf22f8b25a6904c59"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_Restart・例外・Log" sheetId="7" r:id="R67816880c12f4ee5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_単体テスト観点" sheetId="8" r:id="R2a7f68cd2fb348f6"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1167,7 +1167,7 @@
         <x:v>版数</x:v>
       </x:c>
       <x:c r="F16" s="22" t="str">
-        <x:v>Ver.1.3</x:v>
+        <x:v>Ver.1.4</x:v>
       </x:c>
       <x:c r="G16" s="22"/>
       <x:c r="H16" s="22"/>
@@ -1267,7 +1267,7 @@
     </x:row>
     <x:row r="23" ht="100" customHeight="1">
       <x:c r="B23" s="29" t="str">
-        <x:v>文書状態：Review済／承認待ち。二次Review日：2026-09-30。
+        <x:v>文書状態：修正済／Review待ち。改訂日：2026-10-15。
 本ファイルを複製し黄色セルを担当Batchへ置換する。Batch → StepでSQL／TX／Lock／例外／UTへTraceする。基本仕様は正本参照、Class／Method名は任意。非対象のI/O・処理・試験行は削除可。既存仕様を独自変更しない。</x:v>
       </x:c>
       <x:c r="C23" s="29"/>
@@ -1491,7 +1491,7 @@
         <x:v>版数</x:v>
       </x:c>
       <x:c r="C4" s="39" t="str">
-        <x:v>Ver.1.3</x:v>
+        <x:v>Ver.1.4</x:v>
       </x:c>
       <x:c r="D4" s="39"/>
       <x:c r="E4" s="39"/>
@@ -1746,6 +1746,32 @@
       <x:c r="J13"/>
       <x:c r="K13"/>
       <x:c r="L13"/>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="108" t="str">
+        <x:v>Ver.1.4</x:v>
+      </x:c>
+      <x:c r="B14" s="130" t="str">
+        <x:v>2026-10-15</x:v>
+      </x:c>
+      <x:c r="C14" s="108" t="str">
+        <x:v>改訂</x:v>
+      </x:c>
+      <x:c r="D14" s="108" t="str">
+        <x:v>起動・再実行の適用条件と正本位置の記載方式を明確化。</x:v>
+      </x:c>
+      <x:c r="E14" s="108" t="str">
+        <x:v>Project Leader</x:v>
+      </x:c>
+      <x:c r="F14" s="108" t="str">
+        <x:v>－</x:v>
+      </x:c>
+      <x:c r="G14" s="108" t="str">
+        <x:v>－</x:v>
+      </x:c>
+      <x:c r="H14" s="108" t="str">
+        <x:v>Review待ち</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -1913,7 +1939,7 @@
         <x:v>版数</x:v>
       </x:c>
       <x:c r="C4" s="39" t="str">
-        <x:v>Ver.1.3</x:v>
+        <x:v>Ver.1.4</x:v>
       </x:c>
       <x:c r="D4" s="39"/>
       <x:c r="E4" s="39"/>
@@ -1935,13 +1961,13 @@
     </x:row>
     <x:row r="5" ht="22" customHeight="1">
       <x:c r="A5" s="21" t="str">
-        <x:v>基本設計参照</x:v>
+        <x:v>適用する起動時刻、営業日、先行・後続Job、再実行条件を具体的に記載する。該当しない項目は「非対象」と根拠を明示する。基本設計File／Sheet／Batch ID又はCell位置を参照する。</x:v>
       </x:c>
       <x:c r="B5" s="21" t="str">
         <x:v>基本設計参照</x:v>
       </x:c>
       <x:c r="C5" s="39" t="str">
-        <x:v>&lt;&lt;基本設計書番号／Sheet／行&gt;&gt;</x:v>
+        <x:v>&lt;&lt;基本設計File／Sheet／Batch ID又はCell位置&gt;&gt;</x:v>
       </x:c>
       <x:c r="D5" s="39" t="str">
         <x:v>&lt;&lt;基本設計書番号／Sheet／行&gt;&gt;</x:v>
@@ -2900,7 +2926,7 @@
         <x:v>版数</x:v>
       </x:c>
       <x:c r="C4" s="39" t="str">
-        <x:v>Ver.1.3</x:v>
+        <x:v>Ver.1.4</x:v>
       </x:c>
       <x:c r="D4" s="39"/>
       <x:c r="E4" s="39"/>
@@ -2928,7 +2954,7 @@
         <x:v>基本設計参照</x:v>
       </x:c>
       <x:c r="C5" s="39" t="str">
-        <x:v>&lt;&lt;基本設計書番号／Sheet／行&gt;&gt;</x:v>
+        <x:v>&lt;&lt;基本設計File／Sheet／Batch ID又はCell位置&gt;&gt;</x:v>
       </x:c>
       <x:c r="D5" s="39" t="str">
         <x:v>&lt;&lt;基本設計書番号／Sheet／行&gt;&gt;</x:v>
@@ -4159,7 +4185,7 @@
         <x:v>版数</x:v>
       </x:c>
       <x:c r="C4" s="39" t="str">
-        <x:v>Ver.1.3</x:v>
+        <x:v>Ver.1.4</x:v>
       </x:c>
       <x:c r="D4" s="39"/>
       <x:c r="E4" s="39"/>
@@ -4187,7 +4213,7 @@
         <x:v>基本設計参照</x:v>
       </x:c>
       <x:c r="C5" s="39" t="str">
-        <x:v>&lt;&lt;基本設計書番号／Sheet／行&gt;&gt;</x:v>
+        <x:v>&lt;&lt;基本設計File／Sheet／Batch ID又はCell位置&gt;&gt;</x:v>
       </x:c>
       <x:c r="D5" s="39" t="str">
         <x:v>&lt;&lt;基本設計書番号／Sheet／行&gt;&gt;</x:v>
@@ -5723,7 +5749,7 @@
         <x:v>版数</x:v>
       </x:c>
       <x:c r="C4" s="39" t="str">
-        <x:v>Ver.1.3</x:v>
+        <x:v>Ver.1.4</x:v>
       </x:c>
       <x:c r="D4" s="39"/>
       <x:c r="E4" s="39"/>
@@ -5751,7 +5777,7 @@
         <x:v>基本設計参照</x:v>
       </x:c>
       <x:c r="C5" s="39" t="str">
-        <x:v>&lt;&lt;基本設計書番号／Sheet／行&gt;&gt;</x:v>
+        <x:v>&lt;&lt;基本設計File／Sheet／Batch ID又はCell位置&gt;&gt;</x:v>
       </x:c>
       <x:c r="D5" s="39" t="str">
         <x:v>&lt;&lt;基本設計書番号／Sheet／行&gt;&gt;</x:v>
@@ -7598,7 +7624,7 @@
         <x:v>版数</x:v>
       </x:c>
       <x:c r="C4" s="39" t="str">
-        <x:v>Ver.1.3</x:v>
+        <x:v>Ver.1.4</x:v>
       </x:c>
       <x:c r="D4" s="39"/>
       <x:c r="E4" s="39"/>
@@ -7626,7 +7652,7 @@
         <x:v>基本設計参照</x:v>
       </x:c>
       <x:c r="C5" s="39" t="str">
-        <x:v>&lt;&lt;基本設計書番号／Sheet／行&gt;&gt;</x:v>
+        <x:v>&lt;&lt;基本設計File／Sheet／Batch ID又はCell位置&gt;&gt;</x:v>
       </x:c>
       <x:c r="D5" s="39" t="str">
         <x:v>&lt;&lt;基本設計書番号／Sheet／行&gt;&gt;</x:v>
@@ -9035,7 +9061,7 @@
         <x:v>版数</x:v>
       </x:c>
       <x:c r="C4" s="39" t="str">
-        <x:v>Ver.1.3</x:v>
+        <x:v>Ver.1.4</x:v>
       </x:c>
       <x:c r="D4" s="39"/>
       <x:c r="E4" s="39"/>
@@ -9063,7 +9089,7 @@
         <x:v>基本設計参照</x:v>
       </x:c>
       <x:c r="C5" s="39" t="str">
-        <x:v>&lt;&lt;基本設計書番号／Sheet／行&gt;&gt;</x:v>
+        <x:v>&lt;&lt;基本設計File／Sheet／Batch ID又はCell位置&gt;&gt;</x:v>
       </x:c>
       <x:c r="D5" s="39" t="str">
         <x:v>&lt;&lt;基本設計書番号／Sheet／行&gt;&gt;</x:v>
